--- a/Data/Second_part_GBD.xlsx
+++ b/Data/Second_part_GBD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rayanaloliet/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jw12513/git/GWAS-GBD/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D41CBC3A-3ABA-FC4F-BC02-D433E913CCF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762869A9-C41E-0F42-B67E-E19305584816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="500" windowWidth="25300" windowHeight="14600" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="307" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="298">
   <si>
     <t>GBD term</t>
   </si>
@@ -893,6 +893,27 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Other endocrine, metabolic, blood, and immune disorders</t>
+  </si>
+  <si>
+    <t>Crohn's disease</t>
+  </si>
+  <si>
+    <t>Ulcerative colitis</t>
+  </si>
+  <si>
+    <t>Thyroid diseases</t>
+  </si>
+  <si>
+    <t>EFO:0000384</t>
+  </si>
+  <si>
+    <t>EFO:0000729</t>
+  </si>
+  <si>
+    <t>EFO:1000627</t>
   </si>
 </sst>
 </file>
@@ -916,12 +937,18 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -936,11 +963,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1245,10 +1273,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N89"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="35.6640625" customWidth="1"/>
+    <col min="1" max="1" width="42.6640625" customWidth="1"/>
     <col min="2" max="9" width="22.33203125" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1700,7 +1728,7 @@
       </c>
     </row>
     <row r="34" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A34" t="s">
+      <c r="A34" s="2" t="s">
         <v>118</v>
       </c>
       <c r="B34" t="s">
@@ -2341,6 +2369,47 @@
       </c>
       <c r="C85" t="s">
         <v>289</v>
+      </c>
+    </row>
+    <row r="86" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>291</v>
+      </c>
+      <c r="B86" t="s">
+        <v>121</v>
+      </c>
+      <c r="C86" t="s">
+        <v>124</v>
+      </c>
+      <c r="D86" t="s">
+        <v>125</v>
+      </c>
+      <c r="E86" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="87" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>292</v>
+      </c>
+      <c r="B87" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="88" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>293</v>
+      </c>
+      <c r="B88" t="s">
+        <v>296</v>
+      </c>
+    </row>
+    <row r="89" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>294</v>
+      </c>
+      <c r="B89" t="s">
+        <v>297</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Second_part_GBD.xlsx
+++ b/Data/Second_part_GBD.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10102"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10510"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jw12513/git/GWAS-GBD/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/gh13047/repo/GWAS-GBD/Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762869A9-C41E-0F42-B67E-E19305584816}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F8379A6-2940-BC47-96D3-140ECE43BA6A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="25600" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="880" windowWidth="36000" windowHeight="22500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="318" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="325" uniqueCount="308">
   <si>
     <t>GBD term</t>
   </si>
@@ -508,9 +508,6 @@
     <t>Other chronic respiratory diseases</t>
   </si>
   <si>
-    <t>SNOMED:17097001</t>
-  </si>
-  <si>
     <t>Cirrhosis and other chronic liver diseases</t>
   </si>
   <si>
@@ -763,9 +760,6 @@
     <t>Refraction disorders</t>
   </si>
   <si>
-    <t>SNOMED:39021009</t>
-  </si>
-  <si>
     <t>Other mental disorders</t>
   </si>
   <si>
@@ -814,9 +808,6 @@
     <t>Viral skin diseases</t>
   </si>
   <si>
-    <t>OMIT:0017588</t>
-  </si>
-  <si>
     <t>Benign and in situ intestinal neoplasms</t>
   </si>
   <si>
@@ -914,13 +905,52 @@
   </si>
   <si>
     <t>EFO:1000627</t>
+  </si>
+  <si>
+    <t>MONDO:0002320</t>
+  </si>
+  <si>
+    <t>Orphanet:95711</t>
+  </si>
+  <si>
+    <t>MONDO:0019719</t>
+  </si>
+  <si>
+    <t>MONDO:0005715</t>
+  </si>
+  <si>
+    <t>MONDO:0019636</t>
+  </si>
+  <si>
+    <t>MONDO:0018360</t>
+  </si>
+  <si>
+    <t>HP:0002086</t>
+  </si>
+  <si>
+    <t>EFO:0022941</t>
+  </si>
+  <si>
+    <t>EFO:0011049</t>
+  </si>
+  <si>
+    <t>MONDO:0004892</t>
+  </si>
+  <si>
+    <t>EFO:0007814</t>
+  </si>
+  <si>
+    <t>MONDO:0006858</t>
+  </si>
+  <si>
+    <t>MONDO:0021201</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -931,6 +961,14 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13.5"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -963,12 +1001,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1574,7 +1613,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:8" ht="19" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>84</v>
       </c>
@@ -1584,6 +1623,7 @@
       <c r="C22" t="s">
         <v>85</v>
       </c>
+      <c r="D22" s="3"/>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.2">
       <c r="A23" t="s">
@@ -1789,7 +1829,22 @@
         <v>135</v>
       </c>
       <c r="B37" t="s">
-        <v>134</v>
+        <v>295</v>
+      </c>
+      <c r="C37" t="s">
+        <v>296</v>
+      </c>
+      <c r="D37" t="s">
+        <v>297</v>
+      </c>
+      <c r="E37" t="s">
+        <v>298</v>
+      </c>
+      <c r="F37" t="s">
+        <v>299</v>
+      </c>
+      <c r="G37" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="38" spans="1:12" x14ac:dyDescent="0.2">
@@ -1889,491 +1944,497 @@
         <v>161</v>
       </c>
       <c r="B45" t="s">
-        <v>162</v>
+        <v>301</v>
+      </c>
+      <c r="C45" t="s">
+        <v>302</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A46" t="s">
+        <v>162</v>
+      </c>
+      <c r="B46" t="s">
         <v>163</v>
       </c>
-      <c r="B46" t="s">
+      <c r="C46" t="s">
         <v>164</v>
       </c>
-      <c r="C46" t="s">
+      <c r="D46" t="s">
         <v>165</v>
       </c>
-      <c r="D46" t="s">
+      <c r="E46" t="s">
         <v>166</v>
       </c>
-      <c r="E46" t="s">
+      <c r="F46" t="s">
         <v>167</v>
-      </c>
-      <c r="F46" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A47" t="s">
+        <v>168</v>
+      </c>
+      <c r="B47" t="s">
         <v>169</v>
       </c>
-      <c r="B47" t="s">
+      <c r="C47" t="s">
         <v>170</v>
       </c>
-      <c r="C47" t="s">
+      <c r="D47" t="s">
         <v>171</v>
-      </c>
-      <c r="D47" t="s">
-        <v>172</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A48" t="s">
+        <v>172</v>
+      </c>
+      <c r="B48" t="s">
         <v>173</v>
       </c>
-      <c r="B48" t="s">
+      <c r="C48" t="s">
         <v>174</v>
-      </c>
-      <c r="C48" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A49" t="s">
+        <v>175</v>
+      </c>
+      <c r="B49" t="s">
         <v>176</v>
       </c>
-      <c r="B49" t="s">
+      <c r="C49" t="s">
         <v>177</v>
       </c>
-      <c r="C49" t="s">
+      <c r="D49" t="s">
         <v>178</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>179</v>
-      </c>
-      <c r="E49" t="s">
-        <v>180</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A50" t="s">
+        <v>180</v>
+      </c>
+      <c r="B50" t="s">
         <v>181</v>
       </c>
-      <c r="B50" t="s">
+      <c r="C50" t="s">
         <v>182</v>
       </c>
-      <c r="C50" t="s">
+      <c r="D50" t="s">
         <v>183</v>
-      </c>
-      <c r="D50" t="s">
-        <v>184</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A51" t="s">
+        <v>184</v>
+      </c>
+      <c r="B51" t="s">
         <v>185</v>
       </c>
-      <c r="B51" t="s">
+      <c r="C51" t="s">
         <v>186</v>
       </c>
-      <c r="C51" t="s">
+      <c r="D51" t="s">
         <v>187</v>
       </c>
-      <c r="D51" t="s">
+      <c r="E51" t="s">
         <v>188</v>
       </c>
-      <c r="E51" t="s">
-        <v>189</v>
-      </c>
       <c r="F51" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="L51" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A52" t="s">
+        <v>189</v>
+      </c>
+      <c r="B52" t="s">
         <v>190</v>
       </c>
-      <c r="B52" t="s">
+      <c r="C52" t="s">
         <v>191</v>
       </c>
-      <c r="C52" t="s">
+      <c r="D52" t="s">
         <v>192</v>
-      </c>
-      <c r="D52" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A53" t="s">
+        <v>193</v>
+      </c>
+      <c r="B53" t="s">
         <v>194</v>
       </c>
-      <c r="B53" t="s">
+      <c r="C53" t="s">
         <v>195</v>
-      </c>
-      <c r="C53" t="s">
-        <v>196</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A54" t="s">
+        <v>196</v>
+      </c>
+      <c r="B54" t="s">
         <v>197</v>
-      </c>
-      <c r="B54" t="s">
-        <v>198</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A55" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B55" t="s">
-        <v>101</v>
+        <v>303</v>
       </c>
     </row>
     <row r="56" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A56" t="s">
+        <v>199</v>
+      </c>
+      <c r="B56" t="s">
         <v>200</v>
       </c>
-      <c r="B56" t="s">
+      <c r="C56" t="s">
         <v>201</v>
       </c>
-      <c r="C56" t="s">
+      <c r="D56" t="s">
         <v>202</v>
-      </c>
-      <c r="D56" t="s">
-        <v>203</v>
       </c>
     </row>
     <row r="57" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A57" t="s">
+        <v>203</v>
+      </c>
+      <c r="B57" t="s">
         <v>204</v>
       </c>
-      <c r="B57" t="s">
+      <c r="C57" t="s">
         <v>205</v>
       </c>
-      <c r="C57" t="s">
+      <c r="D57" t="s">
         <v>206</v>
       </c>
-      <c r="D57" t="s">
+      <c r="E57" t="s">
         <v>207</v>
       </c>
-      <c r="E57" t="s">
+      <c r="F57" t="s">
         <v>208</v>
       </c>
-      <c r="F57" t="s">
+      <c r="G57" t="s">
         <v>209</v>
       </c>
-      <c r="G57" t="s">
-        <v>210</v>
-      </c>
       <c r="H57" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
     </row>
     <row r="58" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A58" t="s">
+        <v>210</v>
+      </c>
+      <c r="B58" t="s">
         <v>211</v>
       </c>
-      <c r="B58" t="s">
+      <c r="C58" t="s">
         <v>212</v>
       </c>
-      <c r="C58" t="s">
+      <c r="D58" t="s">
         <v>213</v>
-      </c>
-      <c r="D58" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A59" t="s">
+        <v>214</v>
+      </c>
+      <c r="B59" t="s">
         <v>215</v>
       </c>
-      <c r="B59" t="s">
+      <c r="C59" t="s">
         <v>216</v>
-      </c>
-      <c r="C59" t="s">
-        <v>217</v>
       </c>
     </row>
     <row r="60" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A60" t="s">
+        <v>217</v>
+      </c>
+      <c r="B60" t="s">
         <v>218</v>
-      </c>
-      <c r="B60" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="61" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A61" t="s">
+        <v>219</v>
+      </c>
+      <c r="B61" t="s">
         <v>220</v>
       </c>
-      <c r="B61" t="s">
+      <c r="C61" t="s">
         <v>221</v>
-      </c>
-      <c r="C61" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="62" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A62" t="s">
+        <v>222</v>
+      </c>
+      <c r="B62" t="s">
         <v>223</v>
-      </c>
-      <c r="B62" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="63" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A63" t="s">
+        <v>224</v>
+      </c>
+      <c r="B63" t="s">
         <v>225</v>
       </c>
-      <c r="B63" t="s">
+      <c r="C63" t="s">
         <v>226</v>
-      </c>
-      <c r="C63" t="s">
-        <v>227</v>
       </c>
     </row>
     <row r="64" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A64" t="s">
+        <v>227</v>
+      </c>
+      <c r="B64" t="s">
         <v>228</v>
-      </c>
-      <c r="B64" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A65" t="s">
+        <v>229</v>
+      </c>
+      <c r="B65" t="s">
         <v>230</v>
       </c>
-      <c r="B65" t="s">
+      <c r="C65" t="s">
         <v>231</v>
       </c>
-      <c r="C65" t="s">
+      <c r="D65" t="s">
         <v>232</v>
       </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>233</v>
-      </c>
-      <c r="E65" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A66" t="s">
+        <v>234</v>
+      </c>
+      <c r="B66" t="s">
         <v>235</v>
-      </c>
-      <c r="B66" t="s">
-        <v>236</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A67" t="s">
+        <v>236</v>
+      </c>
+      <c r="B67" t="s">
         <v>237</v>
-      </c>
-      <c r="B67" t="s">
-        <v>238</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A68" t="s">
+        <v>238</v>
+      </c>
+      <c r="B68" t="s">
         <v>239</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>240</v>
       </c>
-      <c r="C68" t="s">
+      <c r="D68" t="s">
         <v>241</v>
-      </c>
-      <c r="D68" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A69" t="s">
+        <v>242</v>
+      </c>
+      <c r="B69" t="s">
         <v>243</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>244</v>
-      </c>
-      <c r="C69" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A70" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B70" t="s">
-        <v>247</v>
+        <v>304</v>
+      </c>
+      <c r="C70" t="s">
+        <v>305</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A71" t="s">
+        <v>246</v>
+      </c>
+      <c r="B71" t="s">
+        <v>247</v>
+      </c>
+      <c r="C71" t="s">
         <v>248</v>
       </c>
-      <c r="B71" t="s">
+      <c r="D71" t="s">
         <v>249</v>
-      </c>
-      <c r="C71" t="s">
-        <v>250</v>
-      </c>
-      <c r="D71" t="s">
-        <v>251</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A72" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="B72" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A73" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="B73" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A74" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="B74" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A75" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="B75" t="s">
-        <v>255</v>
+        <v>306</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A76" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="B76" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A77" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="B77" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A78" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B78" t="s">
-        <v>264</v>
+        <v>307</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A79" t="s">
+        <v>262</v>
+      </c>
+      <c r="B79" t="s">
+        <v>263</v>
+      </c>
+      <c r="C79" t="s">
+        <v>264</v>
+      </c>
+      <c r="D79" t="s">
         <v>265</v>
-      </c>
-      <c r="B79" t="s">
-        <v>266</v>
-      </c>
-      <c r="C79" t="s">
-        <v>267</v>
-      </c>
-      <c r="D79" t="s">
-        <v>268</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.2">
       <c r="A80" t="s">
+        <v>266</v>
+      </c>
+      <c r="B80" t="s">
+        <v>267</v>
+      </c>
+      <c r="C80" t="s">
+        <v>268</v>
+      </c>
+      <c r="D80" t="s">
         <v>269</v>
       </c>
-      <c r="B80" t="s">
+      <c r="E80" t="s">
         <v>270</v>
       </c>
-      <c r="C80" t="s">
+      <c r="F80" t="s">
         <v>271</v>
       </c>
-      <c r="D80" t="s">
+      <c r="G80" t="s">
         <v>272</v>
-      </c>
-      <c r="E80" t="s">
-        <v>273</v>
-      </c>
-      <c r="F80" t="s">
-        <v>274</v>
-      </c>
-      <c r="G80" t="s">
-        <v>275</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A81" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="B81" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="C81" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A82" t="s">
+        <v>276</v>
+      </c>
+      <c r="B82" t="s">
+        <v>277</v>
+      </c>
+      <c r="C82" t="s">
+        <v>278</v>
+      </c>
+      <c r="D82" t="s">
         <v>279</v>
       </c>
-      <c r="B82" t="s">
+      <c r="E82" t="s">
         <v>280</v>
-      </c>
-      <c r="C82" t="s">
-        <v>281</v>
-      </c>
-      <c r="D82" t="s">
-        <v>282</v>
-      </c>
-      <c r="E82" t="s">
-        <v>283</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A83" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="B83" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A84" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="B84" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A85" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="B85" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="C85" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A86" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="B86" t="s">
         <v>121</v>
@@ -2390,26 +2451,26 @@
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A87" t="s">
+        <v>289</v>
+      </c>
+      <c r="B87" t="s">
         <v>292</v>
-      </c>
-      <c r="B87" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A88" t="s">
+        <v>290</v>
+      </c>
+      <c r="B88" t="s">
         <v>293</v>
-      </c>
-      <c r="B88" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.2">
       <c r="A89" t="s">
+        <v>291</v>
+      </c>
+      <c r="B89" t="s">
         <v>294</v>
-      </c>
-      <c r="B89" t="s">
-        <v>297</v>
       </c>
     </row>
   </sheetData>
